--- a/artfynd/A 25899-2024 artfynd.xlsx
+++ b/artfynd/A 25899-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112551619</v>
+        <v>112551607</v>
       </c>
       <c r="B2" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379038</v>
+        <v>378758</v>
       </c>
       <c r="R2" t="n">
-        <v>6699024</v>
+        <v>6699180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112551623</v>
+        <v>112551615</v>
       </c>
       <c r="B3" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>378716</v>
+        <v>378993</v>
       </c>
       <c r="R3" t="n">
-        <v>6699384</v>
+        <v>6699264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112551615</v>
+        <v>112551623</v>
       </c>
       <c r="B4" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>378993</v>
+        <v>378716</v>
       </c>
       <c r="R4" t="n">
-        <v>6699265</v>
+        <v>6699384</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112551621</v>
+        <v>112551619</v>
       </c>
       <c r="B5" t="n">
-        <v>78767</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,12 +1071,7 @@
         <v>112551617</v>
       </c>
       <c r="B6" t="n">
-        <v>55732</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379056</v>
+        <v>379055</v>
       </c>
       <c r="R6" t="n">
-        <v>6699058</v>
+        <v>6699059</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1171,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112551621</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster Gräsviggen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>379038</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6699024</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-08-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-08-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25899-2024 artfynd.xlsx
+++ b/artfynd/A 25899-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551607</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551623</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551615</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551619</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551617</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,8 +1298,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551621</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>